--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484318_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484318_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>E. SIMS SERRA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.0684</v>
+        <v>7.1188</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3648</v>
+        <v>5.9856</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7036</v>
+        <v>1.1332</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2148</v>
+        <v>1.7642</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4177</v>
+        <v>1.3592</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2029</v>
+        <v>0.4051</v>
       </c>
       <c r="J2" t="n">
-        <v>2.914</v>
+        <v>3.612</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3857</v>
+        <v>2.397</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4718</v>
+        <v>1.215</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6992</v>
+        <v>-1.8478</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.968</v>
+        <v>-1.0379</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2688</v>
+        <v>-0.8099</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3441</v>
+        <v>3.3208</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>4.2975</v>
+        <v>3.3208</v>
       </c>
       <c r="S2" t="n">
-        <v>4.674</v>
+        <v>0.5379</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5688</v>
+        <v>0.8778</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1053</v>
+        <v>-0.3399</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1646</v>
+        <v>1.4959</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.1646</v>
+        <v>1.4959</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. SIMS SERRA</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0043</v>
+        <v>6.5074</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1162</v>
+        <v>2.403</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8881</v>
+        <v>4.1045</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7642</v>
+        <v>2.2148</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3592</v>
+        <v>2.4177</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4051</v>
+        <v>-0.2029</v>
       </c>
       <c r="J3" t="n">
-        <v>3.612</v>
+        <v>2.914</v>
       </c>
       <c r="K3" t="n">
-        <v>2.397</v>
+        <v>3.3857</v>
       </c>
       <c r="L3" t="n">
-        <v>1.215</v>
+        <v>-0.4718</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8478</v>
+        <v>-0.6992</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0379</v>
+        <v>-0.968</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8099</v>
+        <v>0.2688</v>
       </c>
       <c r="P3" t="n">
-        <v>3.3208</v>
+        <v>2.3441</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R3" t="n">
-        <v>3.3208</v>
+        <v>4.2975</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5766</v>
+        <v>2.1131</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0083</v>
+        <v>1.607</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.585</v>
+        <v>0.5061</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4959</v>
+        <v>-0.1646</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4959</v>
+        <v>-0.1646</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2161</v>
+        <v>6.0523</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5472</v>
+        <v>3.3561</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6689</v>
+        <v>2.6962</v>
       </c>
       <c r="G4" t="n">
         <v>4.3095</v>
@@ -766,13 +766,13 @@
         <v>2.3441</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7027</v>
+        <v>0.1335</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.0384</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1446</v>
+        <v>0.1719</v>
       </c>
       <c r="V4" t="n">
         <v>1.2186</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.1162</v>
+        <v>4.2084</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2922</v>
+        <v>3.1393</v>
       </c>
       <c r="F5" t="n">
-        <v>0.824</v>
+        <v>1.0691</v>
       </c>
       <c r="G5" t="n">
         <v>3.3736</v>
@@ -844,13 +844,13 @@
         <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8831</v>
+        <v>0.9754</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0306</v>
+        <v>0.8778</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1476</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0.0549</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5451</v>
+        <v>3.8645</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1021</v>
+        <v>1.1103</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6472</v>
+        <v>2.7542</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2424</v>
+        <v>1.9439</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.6567</v>
+        <v>0.7439</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8991</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4819</v>
+        <v>1.4939</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.8982</v>
+        <v>2.0466</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4163</v>
+        <v>-0.5527</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7585</v>
+        <v>-1.3026</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4828</v>
+        <v>1.7527</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9534</v>
+        <v>2.1488</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9534</v>
+        <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3492</v>
+        <v>0.1039</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3798</v>
+        <v>-0.0514</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9694</v>
+        <v>0.1554</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.2616</v>
+        <v>2.9421</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8070000000000001</v>
+        <v>-0.4054</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4546</v>
+        <v>3.3476</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9439</v>
+        <v>0.2424</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7439</v>
+        <v>-2.6567</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>2.8991</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4939</v>
+        <v>-0.4819</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0466</v>
+        <v>-1.8982</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5527</v>
+        <v>1.4163</v>
       </c>
       <c r="M7" t="n">
-        <v>0.45</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3026</v>
+        <v>-0.7585</v>
       </c>
       <c r="O7" t="n">
-        <v>1.7527</v>
+        <v>1.4828</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1488</v>
+        <v>1.9534</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1488</v>
+        <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.499</v>
+        <v>0.7463</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3548</v>
+        <v>0.0765</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1442</v>
+        <v>0.6698</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6843</v>
+        <v>2.4877</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1383</v>
+        <v>1.8055</v>
       </c>
       <c r="F8" t="n">
-        <v>0.546</v>
+        <v>0.6822</v>
       </c>
       <c r="G8" t="n">
         <v>1.7927</v>
@@ -1078,13 +1078,13 @@
         <v>2.5395</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0303</v>
+        <v>0.7731</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1899</v>
+        <v>0.8571</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2202</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6642</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2719</v>
+        <v>2.2908</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4467</v>
+        <v>-1.5366</v>
       </c>
       <c r="F9" t="n">
-        <v>3.7185</v>
+        <v>3.8275</v>
       </c>
       <c r="G9" t="n">
         <v>2.4786</v>
@@ -1156,13 +1156,13 @@
         <v>2.7348</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0114</v>
+        <v>0.0076</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2105</v>
+        <v>-0.3004</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1991</v>
+        <v>0.308</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5961</v>
+        <v>-0.0844</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6573</v>
+        <v>-1.0912</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0612</v>
+        <v>1.0067</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3879</v>
@@ -1234,13 +1234,13 @@
         <v>2.5395</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2058</v>
+        <v>0.7174</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2504</v>
+        <v>0.8165</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0447</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>J. CANAL FERRER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9101</v>
+        <v>-0.5457</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-0.6791</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0249</v>
+        <v>0.1334</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5949</v>
+        <v>-1.2047</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0801</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4852</v>
+        <v>-0.3776</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.8595</v>
+        <v>0.4983</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9404</v>
+        <v>-0.2034</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0809</v>
+        <v>0.7017</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2646</v>
+        <v>-1.703</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1397</v>
+        <v>-0.6237</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4043</v>
+        <v>-1.0793</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7814</v>
+        <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3993</v>
+        <v>0.659</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9245</v>
+        <v>0.7759</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4748</v>
+        <v>-0.117</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. CANAL FERRER</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0864</v>
+        <v>-1.9641</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0836</v>
+        <v>-1.7439</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0028</v>
+        <v>-0.2202</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2047</v>
+        <v>-1.5949</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-2.0801</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3776</v>
+        <v>0.4852</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4983</v>
+        <v>-1.8595</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2034</v>
+        <v>-1.9404</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7017</v>
+        <v>0.0809</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.703</v>
+        <v>0.2646</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6237</v>
+        <v>-0.1397</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0793</v>
+        <v>0.4043</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1183</v>
+        <v>0.3453</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3715</v>
+        <v>0.1156</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2532</v>
+        <v>0.2297</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>32.57530000000001</v>
+        <v>32.8778</v>
       </c>
       <c r="E13" t="n">
-        <v>12.041</v>
+        <v>12.3436</v>
       </c>
       <c r="F13" t="n">
-        <v>20.53419999999999</v>
+        <v>20.5344</v>
       </c>
       <c r="G13" t="n">
         <v>13.9322</v>
@@ -1450,7 +1450,7 @@
         <v>8.0991</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.6173</v>
+        <v>-5.617300000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-8.9818</v>
@@ -1468,13 +1468,13 @@
         <v>26.3713</v>
       </c>
       <c r="S13" t="n">
-        <v>6.8097</v>
+        <v>7.1125</v>
       </c>
       <c r="T13" t="n">
-        <v>5.311200000000001</v>
+        <v>5.614</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4983</v>
+        <v>1.4985</v>
       </c>
       <c r="V13" t="n">
         <v>0.1126</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1578</v>
+        <v>2.8664</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9973</v>
+        <v>1.0873</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1605</v>
+        <v>1.7792</v>
       </c>
       <c r="G14" t="n">
         <v>0.1097</v>
@@ -1546,13 +1546,13 @@
         <v>2.3441</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2397</v>
+        <v>-0.0517</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.0834</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2463</v>
+        <v>-0.135</v>
       </c>
       <c r="V14" t="n">
         <v>1.441</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5283</v>
+        <v>0.0421</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6226</v>
+        <v>0.2181</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.176</v>
       </c>
       <c r="G15" t="n">
         <v>0.6784</v>
@@ -1624,13 +1624,13 @@
         <v>0.586</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5178</v>
+        <v>0.0316</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3715</v>
+        <v>-0.033</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1463</v>
+        <v>0.0646</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2772</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3108</v>
+        <v>-1.397</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0882</v>
+        <v>-1.0831</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.399</v>
+        <v>-0.3139</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3207</v>
+        <v>-0.2744</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9147999999999999</v>
+        <v>-0.5574</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5942</v>
+        <v>0.2831</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3964</v>
+        <v>0.0752</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3154</v>
+        <v>-0.6127</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0809</v>
+        <v>0.6879</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0757</v>
+        <v>-0.3496</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.4006</v>
+        <v>0.0553</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6751</v>
+        <v>-0.4049</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.7581</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.038</v>
+        <v>-0.3412</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6219</v>
+        <v>-0.1816</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6599</v>
+        <v>-0.1597</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1646</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3425</v>
+        <v>-2.1354</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0831</v>
+        <v>0.4815</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2594</v>
+        <v>-2.6169</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2744</v>
+        <v>0.3207</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5574</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2831</v>
+        <v>-0.5942</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0752</v>
+        <v>3.3964</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6127</v>
+        <v>3.3154</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6879</v>
+        <v>0.0809</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3496</v>
+        <v>-3.0757</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0553</v>
+        <v>-2.4006</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4049</v>
+        <v>-0.6751</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7814</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2868</v>
+        <v>-0.8626</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1816</v>
+        <v>0.0152</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1052</v>
+        <v>-0.8778</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1646</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.1646</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>A. DIAGNE YADE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2319</v>
+        <v>-2.2241</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.254</v>
+        <v>-0.6683</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0221</v>
+        <v>-1.5558</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8128</v>
+        <v>-1.4194</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1965</v>
+        <v>-0.2865</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0093</v>
+        <v>-1.1328</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2484</v>
+        <v>0.3483</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7601</v>
+        <v>0.9414</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.0085</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5643</v>
+        <v>-1.7676</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5636</v>
+        <v>-1.2279</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0008</v>
+        <v>-0.5397</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0285</v>
+        <v>-0.2187</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0522</v>
+        <v>-0.0399</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.1789</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DIAGNE YADE</t>
+          <t>E. ZUSTOVICH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4808</v>
+        <v>-2.3797</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-2.4563</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6103</v>
+        <v>0.0766</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4194</v>
+        <v>-0.8128</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2865</v>
+        <v>1.1965</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1328</v>
+        <v>-2.0093</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3483</v>
+        <v>-0.2484</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9414</v>
+        <v>1.7601</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-2.0085</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7676</v>
+        <v>-0.5643</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2279</v>
+        <v>-0.5636</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5397</v>
+        <v>-0.0008</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4754</v>
+        <v>-1.1762</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2421</v>
+        <v>-0.2544</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2333</v>
+        <v>-0.9218</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.1286</v>
+        <v>-3.6425</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1132</v>
+        <v>-1.7088</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0154</v>
+        <v>-1.9337</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7042</v>
@@ -2014,13 +2014,13 @@
         <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0571</v>
+        <v>-0.5709</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3026</v>
+        <v>0.1018</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7544</v>
+        <v>-0.6727</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.2811</v>
+        <v>-4.476</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8093</v>
+        <v>-2.3038</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4718</v>
+        <v>-2.1722</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2477</v>
@@ -2092,13 +2092,13 @@
         <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.1582</v>
+        <v>-1.353</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9684</v>
+        <v>-0.4628</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1898</v>
+        <v>-0.8902</v>
       </c>
       <c r="V21" t="n">
         <v>0.0549</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3636</v>
+        <v>-5.3247</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5851</v>
+        <v>-3.3829</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7785</v>
+        <v>-1.9419</v>
       </c>
       <c r="G22" t="n">
         <v>-5.6721</v>
@@ -2170,13 +2170,13 @@
         <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7501</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2943</v>
+        <v>-0.092</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4558</v>
+        <v>-0.6192</v>
       </c>
       <c r="V22" t="n">
         <v>0.2772</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.4816</v>
+        <v>-6.7775</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.34</v>
+        <v>-5.9355</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1416</v>
+        <v>-0.842</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2761</v>
@@ -2248,13 +2248,13 @@
         <v>1.9534</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7675</v>
+        <v>-1.0634</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1499</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6175</v>
+        <v>-0.318</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5545</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.6404</v>
+        <v>-7.127</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.187</v>
+        <v>-4.7826</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4534</v>
+        <v>-2.3444</v>
       </c>
       <c r="G24" t="n">
         <v>-4.6345</v>
@@ -2326,13 +2326,13 @@
         <v>2.1488</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0059</v>
+        <v>-0.4925</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2943</v>
+        <v>0.1102</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7117</v>
+        <v>-0.6027</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2186</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-32.5752</v>
+        <v>-32.5754</v>
       </c>
       <c r="E25" t="n">
-        <v>-20.5341</v>
+        <v>-20.5344</v>
       </c>
       <c r="F25" t="n">
-        <v>-12.0411</v>
+        <v>-12.041</v>
       </c>
       <c r="G25" t="n">
         <v>-13.9324</v>
@@ -2404,13 +2404,13 @@
         <v>14.6506</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.81</v>
+        <v>-6.809799999999999</v>
       </c>
       <c r="T25" t="n">
         <v>-1.4986</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.311299999999999</v>
+        <v>-5.311399999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1125999999999996</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484318_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484318_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.2224</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-1.7183</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.1646</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484318_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-1.8308</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
